--- a/data/KPA_Brazil_Europe_Comparison.xlsx
+++ b/data/KPA_Brazil_Europe_Comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rdrodrig\dev\BRA-EUR_international-BRA-EUR-2025\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068CA6D2-6171-414B-B0E0-C1BE6DBB2091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD8FE69-FA6E-46D8-A30C-B2C252234080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="52">
   <si>
     <t>geographic area (non-oceanic, million km²)</t>
   </si>
@@ -63,18 +63,6 @@
     <t>traffic density (non-oceanic, flights/km²)</t>
   </si>
   <si>
-    <t>Brazil 2019</t>
-  </si>
-  <si>
-    <t>Brazil 2023</t>
-  </si>
-  <si>
-    <t>Europe 2019</t>
-  </si>
-  <si>
-    <t>Europe 2023</t>
-  </si>
-  <si>
     <t>Brazil/Europe 2019</t>
   </si>
   <si>
@@ -112,12 +100,6 @@
   </si>
   <si>
     <t>26.6%</t>
-  </si>
-  <si>
-    <t>Brazil 2024</t>
-  </si>
-  <si>
-    <t>Europe 2024</t>
   </si>
   <si>
     <t>Brazil/Europe 2024</t>
@@ -290,9 +272,6 @@
     </r>
   </si>
   <si>
-    <t>Europe: c.f ACE report</t>
-  </si>
-  <si>
     <t>2 excludes Ukraine, Georgia, Serbia</t>
   </si>
   <si>
@@ -303,6 +282,12 @@
   </si>
   <si>
     <t>1 excludes Ukraine, Georgia, Serbia, Canary Islands &amp; Oceanic areas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Europe  </t>
+  </si>
+  <si>
+    <t>Brazil: c.f Performance report 2024 / Europe: c.f ACE report 2024</t>
   </si>
 </sst>
 </file>
@@ -515,43 +500,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -563,6 +511,41 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color auto="1"/>
@@ -573,7 +556,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -653,15 +636,6 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -690,7 +664,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -702,7 +676,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -725,6 +699,33 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1047,10 +1048,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1082,7 +1083,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B2" s="2">
         <v>2019</v>
@@ -1118,7 +1119,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2">
         <v>2023</v>
@@ -1130,7 +1131,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F3" s="20">
         <v>41</v>
@@ -1154,7 +1155,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B4" s="2">
         <v>2024</v>
@@ -1166,7 +1167,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F4" s="20">
         <v>41</v>
@@ -1188,7 +1189,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B5" s="2">
         <v>2025</v>
@@ -1208,7 +1209,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2">
         <v>2026</v>
@@ -1228,7 +1229,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B7" s="2">
         <v>2027</v>
@@ -1248,7 +1249,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2">
         <v>2019</v>
@@ -1284,7 +1285,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B9" s="2">
         <v>2023</v>
@@ -1320,7 +1321,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B10" s="2">
         <v>2024</v>
@@ -1332,28 +1333,28 @@
         <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G10" s="20">
         <v>57</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I10" s="20">
         <v>10633991</v>
       </c>
       <c r="J10" s="17" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="K10" s="2"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B11" s="2">
         <v>2025</v>
@@ -1373,7 +1374,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B12" s="2">
         <v>2026</v>
@@ -1411,59 +1412,59 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -1477,7 +1478,7 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -1491,7 +1492,7 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -1505,7 +1506,7 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -1518,9 +1519,9 @@
       <c r="K19" s="2"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H24" s="42"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="42"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1532,7 +1533,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" style="3" customWidth="1"/>
@@ -1546,576 +1547,593 @@
     <col min="14" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="4" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="57"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="56" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="57"/>
+      <c r="H1" s="58"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="55"/>
+      <c r="B2" s="4">
+        <v>2019</v>
+      </c>
+      <c r="C2" s="4">
+        <v>2023</v>
+      </c>
+      <c r="D2" s="4">
+        <v>2024</v>
+      </c>
+      <c r="E2" s="60"/>
+      <c r="F2" s="4">
+        <v>2019</v>
+      </c>
+      <c r="G2" s="4">
+        <v>2023</v>
+      </c>
+      <c r="H2" s="4">
+        <v>2024</v>
+      </c>
+      <c r="I2" s="25"/>
+      <c r="J2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="25"/>
-      <c r="J1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="8">
+      <c r="K2" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="32.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="8">
         <v>8.5</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C3" s="8">
         <v>8.5</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D3" s="27">
         <v>8.5</v>
       </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="29">
+      <c r="E3" s="61"/>
+      <c r="F3" s="29">
         <v>10.9</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G3" s="8">
         <v>10.9</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H3" s="8">
         <v>10.9</v>
       </c>
-      <c r="I2" s="8"/>
-      <c r="J2" s="10">
+      <c r="I3" s="8"/>
+      <c r="J3" s="10">
         <v>0.74</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K3" s="10">
         <v>0.74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="9">
-        <v>1</v>
-      </c>
-      <c r="C3" s="9">
-        <v>1</v>
-      </c>
-      <c r="D3" s="28">
-        <v>1</v>
-      </c>
-      <c r="E3" s="32"/>
-      <c r="F3" s="30">
-        <v>37</v>
-      </c>
-      <c r="G3" s="9">
-        <v>37</v>
-      </c>
-      <c r="H3" s="9">
-        <v>37</v>
-      </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B4" s="9">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9">
+        <v>1</v>
+      </c>
+      <c r="D4" s="28">
+        <v>1</v>
+      </c>
+      <c r="E4" s="53"/>
+      <c r="F4" s="30">
+        <v>37</v>
+      </c>
+      <c r="G4" s="9">
+        <v>37</v>
+      </c>
+      <c r="H4" s="9">
+        <v>37</v>
+      </c>
+      <c r="I4" s="9"/>
+      <c r="J4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="9">
         <v>59</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="32"/>
-      <c r="F4" s="30">
+      <c r="C5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="53"/>
+      <c r="F5" s="30">
         <v>382</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G5" s="9">
         <v>375</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" s="22"/>
-      <c r="J4" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="12"/>
-    </row>
-    <row r="5" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="9">
-        <v>43</v>
-      </c>
-      <c r="C5" s="9">
-        <v>41</v>
-      </c>
-      <c r="D5" s="28">
-        <v>41</v>
-      </c>
-      <c r="E5" s="32"/>
-      <c r="F5" s="30">
-        <v>262</v>
-      </c>
-      <c r="G5" s="9">
-        <v>268</v>
-      </c>
       <c r="H5" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" s="23"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="14"/>
+        <v>33</v>
+      </c>
+      <c r="I5" s="22"/>
+      <c r="J5" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="12"/>
     </row>
     <row r="6" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B6" s="9">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="C6" s="9">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="D6" s="28">
-        <v>5</v>
-      </c>
-      <c r="E6" s="32"/>
+        <v>41</v>
+      </c>
+      <c r="E6" s="53"/>
       <c r="F6" s="30">
-        <v>57</v>
+        <v>262</v>
       </c>
       <c r="G6" s="9">
-        <v>57</v>
-      </c>
-      <c r="H6" s="9">
-        <v>57</v>
-      </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="16"/>
+        <v>268</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="23"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="14"/>
     </row>
     <row r="7" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B7" s="9">
-        <v>3126</v>
-      </c>
-      <c r="C7" s="21">
-        <v>3677</v>
+        <v>5</v>
+      </c>
+      <c r="C7" s="9">
+        <v>5</v>
       </c>
       <c r="D7" s="28">
-        <v>3890</v>
-      </c>
-      <c r="E7" s="32"/>
+        <v>5</v>
+      </c>
+      <c r="E7" s="53"/>
       <c r="F7" s="30">
-        <v>16870</v>
+        <v>57</v>
       </c>
       <c r="G7" s="9">
-        <v>16973</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="H7" s="9">
+        <v>57</v>
+      </c>
+      <c r="I7" s="24"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="16"/>
     </row>
     <row r="8" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B8" s="9">
-        <v>1594442</v>
+        <v>3126</v>
       </c>
       <c r="C8" s="21">
-        <v>1801109</v>
+        <v>3677</v>
       </c>
       <c r="D8" s="28">
-        <v>1935139</v>
-      </c>
-      <c r="E8" s="32"/>
+        <v>3890</v>
+      </c>
+      <c r="E8" s="53"/>
       <c r="F8" s="30">
-        <v>11085302</v>
+        <v>16870</v>
       </c>
       <c r="G8" s="9">
-        <v>10144258</v>
-      </c>
-      <c r="H8" s="9">
-        <v>10633991</v>
+        <v>16973</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="B9" s="9">
-        <v>510</v>
-      </c>
-      <c r="C9" s="9">
-        <v>490</v>
+        <v>1594442</v>
+      </c>
+      <c r="C9" s="21">
+        <v>1801109</v>
       </c>
       <c r="D9" s="28">
-        <v>497</v>
-      </c>
-      <c r="E9" s="32"/>
+        <v>1935139</v>
+      </c>
+      <c r="E9" s="53"/>
       <c r="F9" s="30">
-        <f>F8/F7</f>
-        <v>657.10148192056909</v>
+        <v>11085302</v>
       </c>
       <c r="G9" s="9">
-        <f>G8/G7</f>
-        <v>597.67029988805746</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>39</v>
+        <v>10144258</v>
+      </c>
+      <c r="H9" s="9">
+        <v>10633991</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="9">
+        <v>510</v>
+      </c>
+      <c r="C10" s="9">
+        <v>490</v>
+      </c>
+      <c r="D10" s="28">
+        <v>497</v>
+      </c>
+      <c r="E10" s="53"/>
+      <c r="F10" s="30">
+        <f>F9/F8</f>
+        <v>657.10148192056909</v>
+      </c>
+      <c r="G10" s="9">
+        <f>G9/G8</f>
+        <v>597.67029988805746</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="8">
+      <c r="I10" s="9"/>
+      <c r="J10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="8">
         <v>0.187</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C11" s="8">
         <v>0.21099999999999999</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D11" s="27">
         <v>0.22700000000000001</v>
       </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="29">
+      <c r="E11" s="54"/>
+      <c r="F11" s="29">
         <v>1.0169999999999999</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G11" s="8">
         <v>0.93</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H11" s="8">
         <v>0.97599999999999998</v>
       </c>
-      <c r="I10" s="8"/>
-      <c r="J10" s="7">
+      <c r="I11" s="8"/>
+      <c r="J11" s="7">
         <v>0.2</v>
       </c>
-      <c r="K10" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="36"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="43"/>
-      <c r="B12" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="36"/>
+      <c r="K11" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="33"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="43"/>
+      <c r="A13" s="40"/>
       <c r="B13" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="36"/>
+        <v>49</v>
+      </c>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="33"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="43"/>
-      <c r="B14" s="50" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="36"/>
+      <c r="A14" s="40"/>
+      <c r="B14" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="33"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="43"/>
-      <c r="B15" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="36"/>
-    </row>
-    <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="34"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="36"/>
+      <c r="A15" s="40"/>
+      <c r="B15" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="33"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="40"/>
+      <c r="B16" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="33"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="34"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="36"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="33"/>
     </row>
     <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="37"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="36"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="33"/>
     </row>
     <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="37"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="36"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="3">
-        <f>(B8/B2)/1000000</f>
+      <c r="A19" s="34"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="33"/>
+    </row>
+    <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="34"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="33"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B24" s="3">
+        <f>(B9/B3)/1000000</f>
         <v>0.18758141176470589</v>
       </c>
-      <c r="C23" s="3">
-        <f>(C8/C2)/1000000</f>
+      <c r="C24" s="3">
+        <f>(C9/C3)/1000000</f>
         <v>0.21189517647058823</v>
       </c>
-      <c r="D23" s="3">
-        <f t="shared" ref="D23:H23" si="0">(D8/D2)/1000000</f>
+      <c r="D24" s="3">
+        <f t="shared" ref="D24:H24" si="0">(D9/D3)/1000000</f>
         <v>0.22766341176470586</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F24" s="3">
         <f t="shared" si="0"/>
         <v>1.0170001834862386</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G24" s="3">
         <f t="shared" si="0"/>
         <v>0.93066587155963298</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H24" s="3">
         <f t="shared" si="0"/>
         <v>0.97559550458715594</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="3">
-        <f>B8/B7</f>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="3">
+        <f>B9/B8</f>
         <v>510.05822136916186</v>
       </c>
-      <c r="C26" s="3">
-        <f>C8/C7</f>
+      <c r="C27" s="3">
+        <f>C9/C8</f>
         <v>489.83111231982593</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="C29" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="40"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C30" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
-    </row>
-    <row r="31" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="C31" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="40"/>
-    </row>
-    <row r="32" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C32" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="40"/>
+    <row r="30" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="C30" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="37"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C31" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+    </row>
+    <row r="32" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="C32" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="37"/>
     </row>
     <row r="33" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C33" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="40"/>
+      <c r="C33" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="37"/>
     </row>
     <row r="34" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C34" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="40"/>
+      <c r="C34" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="37"/>
     </row>
     <row r="35" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C35" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="40"/>
+      <c r="C35" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="37"/>
     </row>
     <row r="36" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C36" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="40"/>
+      <c r="C36" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="37"/>
+    </row>
+    <row r="37" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C37" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="37"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="A11:A15"/>
+  <mergeCells count="21">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="B12:H12"/>
+    <mergeCell ref="A12:A16"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="B15:H15"/>
-    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B16:H16"/>
     <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="C32:E32"/>
     <mergeCell ref="C33:G33"/>
     <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C35:G35"/>
     <mergeCell ref="C18:G18"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="J4:K6"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="J5:K7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" r:id="rId1"/>
